--- a/output/pdf_financials_xlsx/PTE.xlsx
+++ b/output/pdf_financials_xlsx/PTE.xlsx
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.272896</v>
+        <v>-1.272896</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.599214</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.272896</v>
+        <v>-1.272896</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.599214</v>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8.485973</v>
+        <v>-8.485973</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>11.98428</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>462.8409776814609</v>
+        <v>-462.8409776814609</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>-43.69203667070376</v>
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>1.272896</v>
+        <v>-1.272896</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.599214</v>
@@ -53896,10 +53896,10 @@
         </is>
       </c>
       <c r="E453" s="5" t="n">
-        <v>1.272896</v>
+        <v>-1.272896</v>
       </c>
       <c r="F453" s="5" t="n">
-        <v>0.599214</v>
+        <v>-0.599214</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PTE.xlsx
+++ b/output/pdf_financials_xlsx/PTE.xlsx
@@ -934,34 +934,34 @@
         <v>2.736978</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>2.420416</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>3.09759</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>4.251713</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>6.072092</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>4.890909</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>2.693125</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>1.76107</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>1.982744</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>2.258983</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>1.90851</v>
       </c>
     </row>
     <row r="11">
@@ -992,19 +992,19 @@
         <v>-0.980189</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.936677</v>
+        <v>0.516261</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>4.135119</v>
+        <v>1.037529</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>5.243254</v>
+        <v>0.991541</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.448279</v>
+        <v>-3.623813</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2.235195</v>
+        <v>-2.655714</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-1.23463</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.04185</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.042903</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.034096</v>
       </c>
     </row>
     <row r="13">
@@ -2027,13 +2027,13 @@
         <v>-0.625233</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.671813</v>
+        <v>-0.713663</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.952556</v>
+        <v>-0.995459</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.634428</v>
+        <v>-0.668524</v>
       </c>
     </row>
     <row r="28">
@@ -2143,13 +2143,13 @@
         <v>-0.625233</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.671813</v>
+        <v>-0.713663</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.952556</v>
+        <v>-0.995459</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.634428</v>
+        <v>-0.668524</v>
       </c>
     </row>
     <row r="30">
@@ -2201,13 +2201,13 @@
         <v>-25.64673365968433</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-23.39171166704329</v>
+        <v>-24.84887777318557</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-34.73307605020813</v>
+        <v>-36.29744933826897</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-24.37315091669968</v>
+        <v>-25.68303470754086</v>
       </c>
     </row>
     <row r="31">
@@ -2343,46 +2343,46 @@
         <v>0.03256</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.034782</v>
+        <v>0.009782000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.023644</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.191436</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.030725</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.036081</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.103618</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.090518</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.209491</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.517191</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.66836</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.930945</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.49473</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.889729</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.752591</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.655534</v>
@@ -2459,46 +2459,46 @@
         <v>0.03256</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.059782</v>
+        <v>0.034782</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.025566</v>
+        <v>0.04921</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.025566</v>
+        <v>0.217002</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.025566</v>
+        <v>0.056291</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.026473</v>
+        <v>0.062554</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.026473</v>
+        <v>0.130091</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.026852</v>
+        <v>0.11737</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.027033</v>
+        <v>1.236524</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.517191</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.66836</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.930945</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.49473</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.889729</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.752591</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.655534</v>
@@ -3155,46 +3155,46 @@
         <v>0.00441</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.262088</v>
+        <v>0.287088</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.20001</v>
+        <v>0.176366</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.367847</v>
+        <v>0.176411</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.046674</v>
+        <v>0.015949</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.086135</v>
+        <v>0.050054</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.157764</v>
+        <v>0.054146</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.107393</v>
+        <v>0.016875</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.329099</v>
+        <v>0.119608</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>7.808792</v>
+        <v>0.291601</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.054217</v>
+        <v>0.385857</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.019601</v>
+        <v>0.088656</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.777865</v>
+        <v>0.283135</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.979745</v>
+        <v>0.090016</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.04124</v>
+        <v>0.288649</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.184114</v>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -36666,7 +36666,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">

--- a/output/pdf_financials_xlsx/PTE.xlsx
+++ b/output/pdf_financials_xlsx/PTE.xlsx
@@ -2049,49 +2049,49 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.008493000000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.013336</v>
+        <v>0.028364</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.015868</v>
+        <v>0.030517</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.018422</v>
+        <v>0.025048</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.035673</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.029512</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.027967</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.028521</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.061551</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.149506</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.201807</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.188281</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.156318</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.152138</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.151964</v>
       </c>
     </row>
     <row r="29">
@@ -2107,49 +2107,49 @@
         <v>-0.599214</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.08554299999999999</v>
+        <v>-0.07704999999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.223335</v>
+        <v>0.238363</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.713716</v>
+        <v>-0.699067</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.63416</v>
+        <v>-1.627534</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.183915</v>
+        <v>-1.148242</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.657237</v>
+        <v>0.6867490000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.718962</v>
+        <v>0.746929</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.702261</v>
+        <v>-0.67374</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.888014</v>
+        <v>-2.826463</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.655738</v>
+        <v>-2.506232</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.315955</v>
+        <v>-1.114148</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.625233</v>
+        <v>-0.436952</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.713663</v>
+        <v>-0.557345</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.995459</v>
+        <v>-0.843321</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.668524</v>
+        <v>-0.51656</v>
       </c>
     </row>
     <row r="30">
@@ -2165,49 +2165,49 @@
         <v>-43.69203667070376</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2.969708920409454</v>
+        <v>-2.674866117830196</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.18638203391036</v>
+        <v>10.87181400474165</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-29.85754709245801</v>
+        <v>-29.2447218127145</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-118.1777815704101</v>
+        <v>-117.6986081842756</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-40.48303420241329</v>
+        <v>-39.2632242674917</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>14.95918775181892</v>
+        <v>15.63090213937117</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.8208117332094</v>
+        <v>11.24173195116621</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-6.826327817824616</v>
+        <v>-6.549089446774286</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-60.80623454585879</v>
+        <v>-59.51029742694865</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-67.37679751553992</v>
+        <v>-63.58378951197997</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-39.27035219787205</v>
+        <v>-33.2480855048651</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-25.64673365968433</v>
+        <v>-17.92354460827625</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-24.84887777318557</v>
+        <v>-19.406075111777</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-36.29744933826897</v>
+        <v>-30.75003719228851</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-25.68303470754086</v>
+        <v>-19.84495456936072</v>
       </c>
     </row>
     <row r="31">
@@ -6261,22 +6261,22 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.008493000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.028364</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.015868</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.025048</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.035673</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.029512</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -6304,16 +6304,16 @@
         </is>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.188281</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.156318</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.152138</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.151964</v>
       </c>
     </row>
     <row r="101">
@@ -21502,7 +21502,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -24747,7 +24751,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -28805,7 +28813,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -31340,7 +31348,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -36211,7 +36223,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -42517,7 +42533,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -44426,7 +44446,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -45826,7 +45850,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -47430,7 +47458,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -47531,7 +47563,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -49137,7 +49169,11 @@
           <t>Amortization of tangible assets (note 5)</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -49149,10 +49185,10 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>-0.008493000000000001</v>
+        <v>0.008493000000000001</v>
       </c>
       <c r="H406" s="5" t="n">
-        <v>-0.015028</v>
+        <v>0.015028</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -49238,7 +49274,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -49257,7 +49293,7 @@
         </is>
       </c>
       <c r="H407" s="5" t="n">
-        <v>-0.013336</v>
+        <v>0.013336</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
